--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>39 h 27 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>39 h 31 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -1060,26 +1060,26 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>2 × Tempo Traveller (17 seats)</t>
+          <t>Car (4 seats)</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.44pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>8.42pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 48</t>
+          <t>1 h 50</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay. · Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
         </is>
       </c>
     </row>
@@ -1498,32 +1498,36 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>2 × Tempo Traveller (17 seats)</t>
+          <t>Car (4 seats)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.55am</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>11.37pm</t>
+          <t>11.28pm</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>31 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="J28" s="9" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1580,7 +1584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1613,64 +1617,53 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
+          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
           <t>• Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -1678,17 +1671,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>8.10am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1696,17 +1689,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -1714,17 +1707,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
           <t>1.30pm</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>3.44pm</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -1732,7 +1725,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.44pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -1740,9 +1733,9 @@
           <t>4.14pm</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -1755,124 +1748,132 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>4.44pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>4.44pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>56 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Indian Music Experience Museum by now</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>5.40pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>LECTURE DEMONSTRATION</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>LECTURE DEMONSTRATION</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>8.34pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>54 min · 13 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>8.39pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>9.39pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
@@ -1880,91 +1881,20 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.39pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Indian Music Experience Museum</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>8.42pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 13 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>8.47pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>9.47pm</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>10.47pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6316,7 +6246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6346,60 +6276,49 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -6407,17 +6326,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>8.10am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>8.55am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -6425,7 +6344,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -6433,36 +6352,40 @@
           <t>9.25am</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>9.25am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>9.55am</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>9.17am</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Sabha Bengaluru by now</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.55am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6472,24 +6395,24 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -6497,206 +6420,141 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>10.09am</t>
+          <t>11.00am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>10.09am</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>10.29am</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>11.00am</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>10.00pm</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>CLOSING DAY</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>10.29am</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>During “Closing Day” — arrange packed lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>10.00pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>10.10pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>11.10pm</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>Dinner near Sabha Bengaluru (late return)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>11.10pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>11.28pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>18 min · 6 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>12.33am (+1)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>11.37pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>17 min · 6 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>12.42am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7023,7 +6881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7133,17 +6991,27 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Car (4 seats)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Vehicle estimate for the tour</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
-        <v>137928</v>
+      <c r="B13" s="25" t="n">
+        <v>128928</v>
       </c>
     </row>
   </sheetData>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>39 h 31 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>39 h 51 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.57am (+1) · 4 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.43am (+1) · 4 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 29</t>
+          <t>1 h 39</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1026,22 +1026,18 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 29</t>
+          <t>1 h 39</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
-        </is>
-      </c>
+      <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay. · Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1621,49 +1617,60 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -1671,17 +1678,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1689,17 +1696,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -1707,17 +1714,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>4.14pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -1725,17 +1732,17 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>4.14pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+          <t>4.44pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -1743,158 +1750,139 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.44pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Indian Music Experience Museum</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>56 min · 13 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Indian Music Experience Museum</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>56 min · 13 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>54 min · 13 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>8.39pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>54 min · 13 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>9.39pm</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>8.39pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>9.39pm</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>10.39pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10.39pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9012,7 +9000,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -9029,12 +9017,12 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -9047,12 +9035,12 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -9065,7 +9053,7 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr"/>
@@ -9079,47 +9067,47 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+          <t>10.02pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>42 min · 12 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
+          <t>10.07pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 12 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>11.07pm</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>12.57am (+1)</t>
+          <t>12.07am (+1)</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr"/>
@@ -9142,7 +9130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9172,49 +9160,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -9222,17 +9221,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -9240,17 +9239,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -9258,17 +9257,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>3.48pm</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -9276,17 +9275,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+          <t>4.18pm</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -9294,71 +9293,71 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>4.18pm</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>5.25pm</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
@@ -9366,125 +9365,129 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>10.02pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>42 min · 12 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.07pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
+          <t>11.07pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>Dinner at the stay</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
@@ -9492,43 +9495,18 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>11.52pm</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 12 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>12.57am (+1)</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
+          <t>12.07am (+1)</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>39 h 51 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>40 h 00 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am; Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am; Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 42</t>
+          <t>1 h 51</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1922,7 +1922,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am · Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am · Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2219,55 +2219,59 @@
       <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Meenakshi Rangamancha by now</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2.46pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>3.00pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>14 min · 5 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>15 min · 5 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -2275,48 +2279,44 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr"/>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Meenakshi Rangamancha by now</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -2333,12 +2333,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2351,12 +2351,12 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr"/>
@@ -2383,12 +2383,12 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2398,19 +2398,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>45 min · 13 km · typical traffic for the day</t>
+          <t>55 min · 13 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.10pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.10am (+1)</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>40 h 00 over 15 show days · 1346 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 51 over 15 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.43am (+1) · 4 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.43am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.39pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>44 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -890,7 +890,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am; Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am; Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>“Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
+          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Kecak Performance 5.30pm</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>8.37pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 39</t>
+          <t>1 h 44</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
@@ -1232,16 +1232,16 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2 h 54</t>
+          <t>1 h 25</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>8.35pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>6 Yakshagana artists (local) perform with the group today and travel on their own. · Short night: 6 h 28 between lights out (12.32am (+1)) and wake-up.</t>
+          <t>6 Yakshagana artists (local) perform with the group today and travel on their own.</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am; Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am; Gamelan workshop 5.00pm</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
@@ -1329,11 +1329,11 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 51</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -2662,7 +2662,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Kecak Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2976,69 +2976,69 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>18 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3.14pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>3.59pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>5.31pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>6.01pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>4.29pm</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
           <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>8.30pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3091,12 +3091,12 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3109,7 +3109,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>8.37pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3138,19 +3138,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>41 min · 12 km · typical traffic for the day</t>
+          <t>47 min · 12 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.06pm</t>
+          <t>8.42pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.06pm</t>
+          <t>9.42pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3163,7 +3163,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.06am (+1)</t>
+          <t>10.42pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3212,7 +3212,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -3480,106 +3480,102 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.05pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>45 min · 23 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>2.05pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>3.05pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Mandala Cultural Centre</t>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>51 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>0 min · 0 km</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>4.48pm</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -3587,7 +3583,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -3597,115 +3593,119 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>INDONESIAN × INDIAN SHADOW PUPPETRY PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>9.34pm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>44 min · 23 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.39pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.39pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Dinner near Mandala Cultural Centre (late return)</t>
+          <t>Dinner at the stay</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
@@ -3713,38 +3713,16 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.27pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>37 min · 23 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.32am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>11.39pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3758,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3784,7 +3762,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
     </row>
@@ -3795,49 +3773,60 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 6 h 28 between lights out (12.32am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -3845,17 +3834,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -3863,17 +3852,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -3881,17 +3870,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>2.35pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -3899,17 +3888,17 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+          <t>3.05pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -3917,71 +3906,71 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>3.33pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Chowdiah Memorial Hall</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>18 min · 4 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>3.33pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>4.03pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>4.02pm</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Chowdiah Memorial Hall by now</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>4.05pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>4.32pm</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Chowdiah Memorial Hall</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>17 min · 4 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="D15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.03pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>4.33pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
@@ -3989,17 +3978,17 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>4.33pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
@@ -4007,168 +3996,149 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>6.32pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>TRADITIONAL BALINESE DANCE × YAKSHAGANA PERFORMANCE</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Performance · Chowdiah Memorial Hall, Vyalikaval, Malleshwaram · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Chowdiah Memorial Hall</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Chowdiah Memorial Hall</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>8.35pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>15 min · 4 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.40pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>13 min · 4 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>9.40pm</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>11.08pm</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>10.40pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>12.08am (+1)</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr"/>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4182,7 +4152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4208,7 +4178,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am · Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am · Gamelan workshop 5.00pm</t>
         </is>
       </c>
     </row>
@@ -4476,34 +4446,30 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>4.16pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>29 min · 8 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.53pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
@@ -4511,42 +4477,42 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>4.16pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>9 min · 2 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.25pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.35pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>29 min · 7 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
@@ -4565,17 +4531,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.35pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -4583,182 +4549,146 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>5.29pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>5.44pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>GAMELAN WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>GAMELAN WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
-        </is>
-      </c>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.47pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>27 min · 6 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr"/>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr"/>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>8.52pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>9.52pm</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>8.47pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>27 min · 6 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>8.52pm</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>9.52pm</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
           <t>10.52pm</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7604,7 +7534,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7640,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.05pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -7723,12 +7653,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>2.05pm</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
           <t>2.35pm</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>3.05pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7741,12 +7671,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.10pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7777,12 +7707,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
+          <t>3.10pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
           <t>3.40pm</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>4.10pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7795,12 +7725,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>3.40pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>4.10pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>4.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7813,12 +7743,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.10pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.10pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7831,12 +7761,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.10pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -7849,12 +7779,12 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -7871,12 +7801,12 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -7889,12 +7819,12 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -7907,7 +7837,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -7921,12 +7851,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.39pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -7936,19 +7866,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>19 min · 5 km · typical traffic for the day</t>
+          <t>20 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.44pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -7961,7 +7891,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.44pm</t>
+          <t>10.15pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8010,14 +7940,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am · Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am · Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• “Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
+          <t>• “Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8332,12 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
@@ -8424,12 +8354,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 51 over 15 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 52 over 15 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>44 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 39</t>
+          <t>1 h 40</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.47pm</t>
+          <t>8.18pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr"/>
@@ -4639,12 +4639,12 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.47pm</t>
+          <t>8.18pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4654,19 +4654,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>27 min · 6 km · typical traffic for the day</t>
+          <t>28 min · 7 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.23pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.52pm</t>
+          <t>10.23pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h · 33 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h · 33 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7676,61 +7676,61 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
+          <t>3.09pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Orion Mall</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>24 min · 6 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>3.09pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>3.39pm</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
           <t>3.10pm</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Orion Mall</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>25 min · 6 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>3.10pm</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Orion Mall by now</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>3.10pm</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>3.40pm</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+      <c r="D14" s="21" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.39pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.10pm</t>
+          <t>4.09pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7743,12 +7743,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.10pm</t>
+          <t>4.09pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.10pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.10pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -8817,12 +8817,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8835,12 +8835,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8871,12 +8871,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8889,12 +8889,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8907,12 +8907,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.59pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -9223,7 +9223,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 52 over 15 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 33 over 15 show days · 1286 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6094,19 +6094,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h · 33 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.55pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>10.20am</t>
+          <t>10.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6313,19 +6313,19 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>16 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>10.20am</t>
+          <t>10.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>10.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6338,7 +6338,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>10.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>39 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>39 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>41 min · 23 km · typical traffic for the day</t>
+          <t>41 min · 23 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 33 over 15 show days · 1286 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 31 over 15 show days · 1286 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>39 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.59am</t>
+          <t>5.57am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7293,12 +7293,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.39am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7311,12 +7311,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.39am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.54am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7329,7 +7329,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.54am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>24 min · 6 km · typical traffic for the day · 10 min loading first</t>
+          <t>24 min · 6 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>20 min · 5 km · typical traffic for the day</t>
+          <t>20 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 31 over 15 show days · 1286 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 17 over 15 show days · 1273 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>3.01pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6094,19 +6094,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.57am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7293,12 +7293,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7311,12 +7311,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7329,7 +7329,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.01pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>41 min · 23 km · traffic, refreshed hourly</t>
+          <t>32 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>21 min · 11 km · typical traffic for the day · 10 min loading first</t>
+          <t>21 min · 11 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 26 km · typical traffic for the day</t>
+          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>48 min · 20 km · typical traffic for the day</t>
+          <t>48 min · 20 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 17 over 15 show days · 1273 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>36 h 52 over 15 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>44 min</t>
+          <t>21 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6094,19 +6094,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>32 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.52am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7293,12 +7293,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7311,12 +7311,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7329,7 +7329,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.09pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7686,19 +7686,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>24 min · 6 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.09pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.39pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7725,12 +7725,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.39pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.09pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7743,12 +7743,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.09pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -7866,19 +7866,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>20 min · 5 km · traffic, refreshed hourly</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -7891,7 +7891,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.15pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>36 h 52 over 15 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>36 h 08 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.43am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.33am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>38 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.38pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 10</t>
+          <t>1 h 27</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
@@ -1065,12 +1061,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>3.46pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>7.36pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1132,30 +1128,52 @@
       <c r="J19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sat, 10 Oct</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Rest day</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr"/>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Show day</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>2 × Tempo Traveller (17 seats)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>No position for venue “MLA College, Malleswaram” — add it in the venue list.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1606,7 +1624,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1737,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>3.16pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1732,12 +1750,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>3.16pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>3.46pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1750,12 +1768,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>3.46pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1765,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>56 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1790,12 +1808,12 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1812,12 +1830,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1830,12 +1848,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>7.36pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1845,19 +1863,19 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>54 min · 13 km · typical traffic for the day</t>
+          <t>56 min · 13 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>8.39pm</t>
+          <t>7.41pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>9.39pm</t>
+          <t>8.41pm</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1870,7 +1888,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.39pm</t>
+          <t>9.41pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr"/>
@@ -2446,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2472,64 +2490,53 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rest day · no travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• No position for venue “MLA College, Malleswaram” — add it in the venue list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -2537,39 +2544,35 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>8.10am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Rest day — no programme</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Rehearsal, rest or a city visit can be pencilled here.</t>
-        </is>
-      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -2577,17 +2580,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>1.30pm</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -2595,17 +2598,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>2.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -2613,18 +2616,241 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
+          <t>2.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>2.55pm</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at MLA College, Malleswaram by now</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP - 2</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>8.10pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>9.10pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6084,7 +6310,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6094,19 +6320,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6909,7 +7135,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -6929,7 +7155,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>128928</v>
+        <v>134928</v>
       </c>
     </row>
   </sheetData>
@@ -7262,7 +7488,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7272,14 +7498,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>32 min · 19 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.52am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7293,12 +7519,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7311,12 +7537,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7329,7 +7555,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7944,49 +8170,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>6.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -7994,17 +8231,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8012,71 +8249,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>8.01am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>21 min · 11 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>7.56am</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>8.06am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.01am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.11am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8084,17 +8321,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.11am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8102,183 +8339,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.36am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.28pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>38 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.51pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12.58pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.21pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.28pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>1.58pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.51pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8286,17 +8523,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -8304,7 +8541,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -8314,7 +8551,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -8439,7 +8676,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>11.38pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -8449,14 +8686,14 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>48 min · 20 km · traffic, refreshed hourly</t>
+          <t>33 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>12.43am (+1)</t>
+          <t>12.28am (+1)</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr"/>
@@ -8468,9 +8705,6 @@
       <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8850,7 +9084,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>57 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9246,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>42 min · 12 km · typical traffic for the day</t>
+          <t>42 min · 12 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>36 h 08 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>36 h 49 over 16 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.33am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.34am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>38 min</t>
+          <t>41 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>21 min</t>
+          <t>27 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,18 +908,22 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.29pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 27</t>
+          <t>1 h 47</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -6310,7 +6314,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6320,19 +6324,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>41 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.36pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7488,7 +7492,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7498,14 +7502,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.57am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7519,12 +7523,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7537,12 +7541,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7555,7 +7559,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7672,7 +7676,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7682,7 +7686,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>38 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7906,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7912,19 +7916,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>14 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7951,12 +7955,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7969,12 +7973,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7987,7 +7991,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8092,19 +8096,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>13 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.04pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8117,7 +8121,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8170,60 +8174,49 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>6.20am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8231,17 +8224,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.00am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8249,71 +8242,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>7.56am</t>
-        </is>
-      </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>7.58am</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>7.31am</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Drishti Art Centre by now</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7.56am</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>8.06am</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8321,17 +8314,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8339,183 +8332,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>8.33am</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.33am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Spare time at the venue</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.28pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>1.40pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>38 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>12.58pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>50 min · 29 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1.10pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>1.28pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>1.58pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8523,17 +8516,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -8541,7 +8534,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -8551,7 +8544,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -8676,7 +8669,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.29pm</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -8686,14 +8679,14 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic</t>
+          <t>39 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
+          <t>12.34am (+1)</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr"/>
@@ -8705,6 +8698,9 @@
       <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9472,7 +9468,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>58 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9630,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>42 min · 12 km · typical traffic for the day</t>
+          <t>42 min · 12 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>36 h 49 over 16 show days · 1285 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>35 h 37 over 16 show days · 1278 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.34am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.33am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>41 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>27 min</t>
+          <t>23 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.29pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 47</t>
+          <t>1 h 33</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -977,17 +973,17 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>9.47pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 39</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1787,7 +1783,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>54 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1863,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>56 min · 13 km · typical traffic for the day</t>
+          <t>56 min · 13 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6310,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6324,19 +6320,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>41 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.36pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7492,7 +7488,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7502,14 +7498,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.57am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7523,12 +7519,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7541,12 +7537,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7559,7 +7555,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7676,7 +7672,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7686,7 +7682,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>38 min · 18 km · live traffic</t>
+          <t>32 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7902,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7916,19 +7912,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7955,12 +7951,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7973,12 +7969,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7991,7 +7987,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8086,7 +8082,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8096,19 +8092,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>13 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8121,7 +8117,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8144,7 +8140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8174,49 +8170,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>6.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8224,17 +8231,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8242,71 +8249,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.58am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>7.57am</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>8.07am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8314,17 +8321,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8332,183 +8339,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.33am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.33pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>43 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.40pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>50 min · 29 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1.03pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.10pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.33pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2.03pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8516,53 +8523,57 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.40pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8571,136 +8582,111 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 21 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.29pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>39 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.34am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.28am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8902,7 +8888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9034,7 +9020,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -9047,12 +9033,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -9063,50 +9049,50 @@
       <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>4.18pm</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>4.29pm</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>5.08pm</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9119,12 +9105,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9137,146 +9123,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>5.43pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>5.43pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>10.02pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>42 min · 12 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.07pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.07pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>9.47pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>27 min · 13 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>12.07am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>9.52pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>10.52pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>11.52pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>35 h 37 over 16 show days · 1278 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>35 h 07 over 16 show days · 1277 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.33am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.32am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 10</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>23 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 33</t>
+          <t>1 h 36</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1017,21 +1017,21 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 40</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.36pm</t>
+          <t>7.37pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 51</t>
+          <t>1 h 52</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>11.28pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>34 min</t>
+          <t>32 min</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>54 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>53 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>7.36pm</t>
+          <t>7.37pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1863,19 +1863,19 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>56 min · 13 km · traffic, refreshed hourly</t>
+          <t>57 min · 13 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.41pm</t>
+          <t>7.42pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.41pm</t>
+          <t>8.42pm</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1888,7 +1888,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.41pm</t>
+          <t>9.42pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>42 min · 16 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2416,19 +2416,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>55 min · 13 km · typical traffic for the day</t>
+          <t>56 min · 13 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6320,19 +6320,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>10.21am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6539,19 +6539,19 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>16 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>10.21am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10.31am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6564,7 +6564,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>10.31am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>11.28pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6677,14 +6677,14 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>18 min · 6 km · typical traffic for the day</t>
+          <t>17 min · 6 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>12.33am (+1)</t>
+          <t>12.32am (+1)</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr"/>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -6906,14 +6906,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>54 min · 33 km · typical traffic for the day</t>
+          <t>55 min · 33 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7498,14 +7498,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 19 km · live traffic · 10 min loading first</t>
+          <t>36 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.56am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7519,12 +7519,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7537,12 +7537,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 17 km · live traffic</t>
+          <t>34 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8092,19 +8092,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.07pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.05pm</t>
+          <t>9.07pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8117,7 +8117,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>10.07pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8303,12 +8303,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8321,12 +8321,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>44 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>1.04pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8487,12 +8487,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8505,12 +8505,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8523,7 +8523,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic</t>
+          <t>34 min · 21 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
+          <t>12.29am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9080,19 +9080,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>29 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9105,12 +9105,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9123,12 +9123,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9246,19 +9246,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic</t>
+          <t>29 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.54pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.52pm</t>
+          <t>10.54pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9271,7 +9271,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.54pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9294,7 +9294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -9439,12 +9439,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -9457,12 +9457,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>58 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9529,146 +9529,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>5.44pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>5.44pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>10.02pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>42 min · 12 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.07pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.07pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>9.49pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>29 min · 13 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>12.07am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>9.54pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>10.54pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>11.54pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>35 h 07 over 16 show days · 1277 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 22 over 16 show days · 1283 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 10</t>
+          <t>1 h 12</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -908,18 +908,22 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 36</t>
+          <t>1 h 38</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -978,12 +982,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1026,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1061,17 +1065,17 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.46pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.37pm</t>
+          <t>7.08pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 50</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1598,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.16pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1750,12 +1754,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.16pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.46pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1768,12 +1772,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.46pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1787,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>53 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>27 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1805,99 +1809,117 @@
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>4.42pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>7.37pm</t>
-        </is>
-      </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 13 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.42pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.42pm</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+          <t>7.08pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>28 min · 13 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.42pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
+          <t>7.13pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>8.13pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.13pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7498,7 +7520,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>36 min · 19 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7694,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7682,7 +7704,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>34 min · 18 km · live traffic</t>
+          <t>36 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8170,60 +8192,49 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>6.20am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8231,17 +8242,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.00am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8249,71 +8260,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>7.58am</t>
-        </is>
-      </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>7.57am</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>7.31am</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Drishti Art Centre by now</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7.58am</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>8.08am</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8321,17 +8332,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8339,183 +8350,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>8.32am</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.32am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Spare time at the venue</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.34pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>1.36pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>44 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>1.04pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>46 min · 26 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1.06pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>1.34pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>2.04pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8523,170 +8534,191 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>2.36pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2.36pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.24pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>34 min · 21 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.29am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.25pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>35 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.30am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9070,7 +9102,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9080,19 +9112,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>29 min · 14 km · live traffic · 10 min loading first</t>
+          <t>31 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9105,12 +9137,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9123,12 +9155,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9141,7 +9173,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9236,7 +9268,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9246,19 +9278,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>29 min · 13 km · live traffic</t>
+          <t>30 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.54pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.54pm</t>
+          <t>10.55pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9271,7 +9303,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.54pm</t>
+          <t>11.55pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9462,7 +9494,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9472,7 +9504,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>29 min · 14 km · live traffic · 10 min loading first</t>
+          <t>31 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9525,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9511,12 +9543,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9529,12 +9561,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9547,7 +9579,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9642,7 +9674,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9652,19 +9684,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>29 min · 13 km · live traffic</t>
+          <t>30 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.54pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.54pm</t>
+          <t>10.55pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9677,7 +9709,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.54pm</t>
+          <t>11.55pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 22 over 16 show days · 1283 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 13 over 16 show days · 1277 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.56pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 12</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>8.01pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>23 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 38</t>
+          <t>1 h 35</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -982,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>56 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>56 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1070,16 +1066,16 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.08pm</t>
+          <t>7.06pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1118,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>7.47pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 52</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1787,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic · 10 min loading first</t>
+          <t>26 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1812,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1875,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.08pm</t>
+          <t>7.06pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1885,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>28 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.13pm</t>
+          <t>7.11pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.13pm</t>
+          <t>8.11pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1910,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2050,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2060,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>42 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>28 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2099,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2117,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2135,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2230,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.46pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2261,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.46pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>14 min · 5 km · traffic, refreshed hourly</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>7.47pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2438,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>56 min · 13 km · traffic, refreshed hourly</t>
+          <t>27 min · 14 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>7.52pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2463,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>9.52pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3008,7 +3004,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>40 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>40 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3220,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>17 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3382,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>47 min · 12 km · typical traffic for the day</t>
+          <t>47 min · 12 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7506,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7520,14 +7516,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.56am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7541,12 +7537,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7559,12 +7555,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7577,7 +7573,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7694,7 +7690,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.56pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7704,7 +7700,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>36 min · 18 km · live traffic</t>
+          <t>33 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7934,19 +7930,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7973,12 +7969,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7991,12 +7987,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8009,7 +8005,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8104,7 +8100,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>8.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8114,19 +8110,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.07pm</t>
+          <t>8.06pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.07pm</t>
+          <t>9.06pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8139,7 +8135,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.07pm</t>
+          <t>10.06pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8162,7 +8158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8192,49 +8188,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>6.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8242,17 +8249,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8260,71 +8267,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7.57am</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>8.07am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8332,17 +8339,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8350,183 +8357,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.32am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.34pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>44 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.36pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>46 min · 26 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1.04pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.06pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.34pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2.04pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8534,53 +8541,57 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.36pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.36pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8589,136 +8600,111 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.24pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>34 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.25pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>35 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.30am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.29am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9102,7 +9088,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9112,19 +9098,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>31 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9137,12 +9123,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9155,12 +9141,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9173,7 +9159,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9268,7 +9254,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9278,19 +9264,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>30 min · 13 km · live traffic</t>
+          <t>28 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.53pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.55pm</t>
+          <t>10.53pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9303,7 +9289,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.55pm</t>
+          <t>11.53pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9494,7 +9480,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9504,7 +9490,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>31 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9511,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9543,12 +9529,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9561,12 +9547,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9579,7 +9565,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9674,7 +9660,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9684,19 +9670,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>30 min · 13 km · live traffic</t>
+          <t>28 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.53pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.55pm</t>
+          <t>10.53pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9709,7 +9695,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.55pm</t>
+          <t>11.53pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 13 over 16 show days · 1277 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>32 h 52 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.01pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>23 min</t>
+          <t>22 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 35</t>
+          <t>1 h 33</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>56 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>56 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.06pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.47pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 25</t>
+          <t>1 h 27</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic · 10 min loading first</t>
+          <t>25 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.06pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.11pm</t>
+          <t>7.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.11pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.10pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>28 min · 12 km · live traffic · 10 min loading first</t>
+          <t>26 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.47pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.52pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>41 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.56am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.56am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>44 min · 23 km · typical traffic for the day</t>
+          <t>45 min · 23 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.39pm</t>
+          <t>9.40pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.39pm</t>
+          <t>10.40pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.39pm</t>
+          <t>11.40pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6338,19 +6338,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 19 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7537,12 +7537,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7555,12 +7555,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7573,7 +7573,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>33 min · 18 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7930,19 +7930,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7969,12 +7969,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7987,12 +7987,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8005,7 +8005,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.01pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8110,19 +8110,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.06pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.06pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8135,7 +8135,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.06pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8303,12 +8303,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8321,12 +8321,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8339,12 +8339,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8484,14 +8484,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>44 min · 29 km · live traffic</t>
+          <t>43 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.04pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8505,12 +8505,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8523,12 +8523,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9098,19 +9098,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9123,12 +9123,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9141,12 +9141,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9264,19 +9264,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>28 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.53pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.53pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9289,7 +9289,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.53pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9511,12 +9511,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9529,12 +9529,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9547,12 +9547,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9565,7 +9565,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9670,19 +9670,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>28 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.53pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.53pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9695,7 +9695,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.53pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>32 h 52 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>32 h 28 over 16 show days · 1273 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 33</t>
+          <t>1 h 28</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1071,11 +1071,11 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.37pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 44</t>
+          <t>1 h 10</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1255,11 +1255,11 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 27</t>
+          <t>1 h 30</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>26 min · 12 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.51pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.20am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>40 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.50am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.20am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.40am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.40am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3205,12 +3205,12 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3220,19 +3220,19 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>17 min · 5 km · traffic, refreshed hourly</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3245,12 +3245,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3277,12 +3277,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.37pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>47 min · 12 km · traffic, refreshed hourly</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.42pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.42pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.42pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>42 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>45 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.55am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.45am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.45am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>10.00am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3626,95 +3626,95 @@
       </c>
       <c r="D13" s="10" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>9.57am</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr"/>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr"/>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -3724,47 +3724,51 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Hold at Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>2.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Lunch near Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>4.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>0 min · 0 km</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -3774,34 +3778,30 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>0 min · 0 km</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -3809,164 +3809,146 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
+      <c r="B28" s="19" t="inlineStr"/>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr"/>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>9.35pm</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>45 min · 23 km · traffic, refreshed hourly</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>9.40pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>45 min · 23 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+          <t>10.40pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.40pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>10.40pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>11.40pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>11.40pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4165,7 +4147,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>18 min · 4 km · typical traffic for the day · 10 min loading first</t>
+          <t>18 min · 4 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4327,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>15 min · 4 km · typical traffic for the day</t>
+          <t>15 min · 4 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4672,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4721,7 +4703,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4736,7 +4718,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>9 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7488,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7516,14 +7498,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7537,12 +7519,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7555,12 +7537,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7573,7 +7555,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7690,7 +7672,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7700,7 +7682,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>31 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8456,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8484,14 +8466,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>12.59pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8505,12 +8487,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8523,12 +8505,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8541,12 +8523,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8676,7 +8658,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8686,14 +8668,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic</t>
+          <t>33 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.29am (+1)</t>
+          <t>12.28am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9088,7 +9070,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9098,19 +9080,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9123,12 +9105,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9141,12 +9123,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9159,7 +9141,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9254,7 +9236,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9264,19 +9246,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9289,7 +9271,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9480,7 +9462,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9490,7 +9472,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9511,12 +9493,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9529,12 +9511,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9547,12 +9529,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9565,7 +9547,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9660,7 +9642,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9670,19 +9652,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9695,7 +9677,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>32 h 28 over 16 show days · 1273 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 31 over 16 show days · 1296 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.32am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.36am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>41 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>27 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,18 +908,22 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.31pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 28</t>
+          <t>1 h 52</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -978,16 +982,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1026,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,16 +1070,16 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.14pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,12 +1118,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 22</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1210,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 10</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1254,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 30</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1347,11 +1351,11 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1773,7 +1777,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1787,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>35 min · 16 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1812,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1875,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.14pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1885,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>34 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.10pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1910,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.10pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2060,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>35 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2081,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2099,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2117,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2135,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2230,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2261,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2428,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2438,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>35 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.51pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2463,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3008,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.48am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3029,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3047,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3065,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3083,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3174,7 +3178,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3205,7 +3209,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -3220,7 +3224,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3376,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3386,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>35 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3411,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3430,7 +3434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3558,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>45 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.48am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3579,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3597,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,110 +3615,110 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
+          <t>9.53am</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>9.53am</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr"/>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr"/>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Hold at Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -3724,51 +3728,47 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>2.20pm</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Lunch near Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Mandala Cultural Centre by now</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>0 min · 0 km</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -3778,30 +3778,34 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>0 min · 0 km</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -3809,146 +3813,164 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8.00pm</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr"/>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.35pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>45 min · 23 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.40pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.40pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>9.27pm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>37 min · 23 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>11.40pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr">
+          <t>9.32pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>10.32pm</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>11.32pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4492,7 +4514,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4502,7 +4524,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>26 min · 8 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4545,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4541,12 +4563,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4559,12 +4581,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4577,7 +4599,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4718,7 +4740,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>8 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4902,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>28 min · 7 km · typical traffic for the day</t>
+          <t>28 min · 8 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6332,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6320,19 +6342,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>41 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.36pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7488,7 +7510,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7498,14 +7520,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.58am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7519,12 +7541,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.28am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.38am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7537,12 +7559,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.38am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7555,7 +7577,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7672,7 +7694,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7682,7 +7704,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 17 km · live traffic</t>
+          <t>37 min · 23 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7924,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7912,19 +7934,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>14 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7951,12 +7973,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7969,12 +7991,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7987,7 +8009,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8082,7 +8104,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8092,19 +8114,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>13 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.04pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8117,7 +8139,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8140,7 +8162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8170,60 +8192,49 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>6.20am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8231,17 +8242,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.00am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8249,71 +8260,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>7.56am</t>
-        </is>
-      </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>7.58am</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>7.31am</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Drishti Art Centre by now</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7.56am</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>8.06am</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8321,17 +8332,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8339,183 +8350,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>8.33am</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.33am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Spare time at the venue</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.29pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>1.43pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>39 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>12.59pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>53 min · 26 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1.13pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>1.29pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>1.59pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>1.43pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8523,170 +8534,191 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2.43pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.23pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>33 min · 20 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.31pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>41 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.36am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9070,7 +9102,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9080,19 +9112,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>42 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9105,12 +9137,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9123,12 +9155,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9141,7 +9173,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9236,7 +9268,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9246,19 +9278,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>35 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>11.00pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9271,7 +9303,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>12.00am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9462,7 +9494,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9472,7 +9504,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>42 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9525,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9511,12 +9543,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9529,12 +9561,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9547,7 +9579,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9642,7 +9674,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9652,19 +9684,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>35 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>11.00pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9677,7 +9709,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>12.00am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 31 over 16 show days · 1296 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>30 h 32 over 16 show days · 1258 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.36am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>41 min</t>
+          <t>38 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>27 min</t>
+          <t>21 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.31pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 52</t>
+          <t>1 h 30</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -982,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.43pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1026,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.43pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1070,16 +1066,16 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.14pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 09</t>
+          <t>49 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1118,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 22</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1210,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.13pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1254,16 +1250,16 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1298,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.35pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>17 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1346,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.18pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1391,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 59</t>
+          <t>2 h 11</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1439,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15 h 36</t>
+          <t>15 h 32</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1477,21 +1473,21 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>12.52pm</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.17pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 51</t>
+          <t>1 h 55</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1512,38 +1508,38 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Car (4 seats)</t>
+          <t>2 × Tempo Traveller (17 seats)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>32 min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
+          <t>No position for venue “Suchitra Cinema and Cultural Academy - Amphitheatre” — add it in the venue list.</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1787,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>35 min · 16 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
           <t>4.40pm</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>4.50pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1812,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1875,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.14pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1885,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>34 min · 12 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.09pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1910,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2050,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2060,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2099,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2117,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2135,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2230,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2261,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2438,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.49pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.49pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2463,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2998,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3008,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.48am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3029,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3047,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3065,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3083,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3178,7 +3174,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3209,7 +3205,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -3224,7 +3220,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.13pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3386,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 12 km · live traffic</t>
+          <t>23 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.18pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3411,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.30pm</t>
+          <t>10.18pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3558,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.48am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3579,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3597,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3615,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3633,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3926,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3936,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 23 km · live traffic</t>
+          <t>28 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.23pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3961,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.32pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4159,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.33pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4169,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>18 min · 4 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.33pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.03pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4192,46 +4188,46 @@
       <c r="D14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>3.53pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>4.23pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>4.02pm</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Chowdiah Memorial Hall by now</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>4.03pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>4.33pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
+      <c r="D16" s="21" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.33pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4244,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4339,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.35pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4349,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>15 min · 4 km · traffic, refreshed hourly</t>
+          <t>9 min · 4 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.40pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.40pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4374,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.40pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4514,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4524,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4563,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4581,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
+          <t>9.16am</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
           <t>9.31am</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4599,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4694,7 +4690,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4725,7 +4721,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4740,7 +4736,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>8 min · 2 km · traffic, refreshed hourly</t>
+          <t>4 min · 2 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.18pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4902,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>28 min · 8 km · traffic, refreshed hourly</t>
+          <t>13 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.23pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4927,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.23pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5071,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5081,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>26 min · 8 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5120,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5138,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5156,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5261,7 +5257,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>29 min · 8 km · typical traffic for the day</t>
+          <t>29 min · 8 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5319,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>35 min · 9 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 10 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5340,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5358,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.27pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5376,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.27pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.27pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5394,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.27pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5517,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5619,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>8 h 04 · 393 km · typical traffic for the day · home about 5.35am (+1)</t>
+          <t>8 h · 393 km · traffic, refreshed hourly · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5977,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>12.28pm</t>
+          <t>12.22pm</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -6012,12 +6008,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.28pm</t>
+          <t>12.22pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>12.52pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6030,7 +6026,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>12.52pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -6045,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>52 min · 15 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 16 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6193,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.17pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6207,19 +6203,19 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>59 min · 13 km · typical traffic for the day</t>
+          <t>57 min · 13 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>7.24pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -6232,7 +6228,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr"/>
@@ -6332,7 +6328,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6342,19 +6338,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>41 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.36pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6412,7 +6408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6438,14 +6434,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
+          <t>• No position for venue “Suchitra Cinema and Cultural Academy - Amphitheatre” — add it in the venue list.</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6511,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -6528,17 +6524,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.55am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -6546,39 +6542,35 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>10.20am</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+          <t>3.05pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>10.20am</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -6586,79 +6578,71 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>11.00am</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
-        </is>
-      </c>
+          <t>→ Leave the stay for Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Suchitra Cinema and Cultural Academy - Amphitheatre by now</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
@@ -6666,56 +6650,146 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>11.27pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>17 min · 6 km · typical traffic for the day</t>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>THE FINALE</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>12.32am (+1)</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>9.35pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>9.40pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>10.40pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>11.40pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7157,7 +7231,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -7167,7 +7241,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -7177,7 +7251,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>134928</v>
+        <v>139428</v>
       </c>
     </row>
   </sheetData>
@@ -7510,7 +7584,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.28am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7520,14 +7594,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.58am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7541,12 +7615,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.28am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.38am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7559,12 +7633,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.38am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7577,7 +7651,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7694,7 +7768,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7704,7 +7778,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>37 min · 23 km · live traffic</t>
+          <t>28 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7998,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7934,19 +8008,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7973,12 +8047,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7991,12 +8065,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8009,7 +8083,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8104,7 +8178,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8114,19 +8188,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>13 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8139,7 +8213,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8162,7 +8236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8192,49 +8266,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>6.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8242,17 +8327,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8260,71 +8345,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.58am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>7.56am</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>8.06am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -8332,17 +8417,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8350,183 +8435,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.33am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.31pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>41 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.43pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>53 min · 26 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1.01pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.13pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.31pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2.01pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.43pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8534,53 +8619,57 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.43pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8589,136 +8678,111 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.31pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>41 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.36am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.28am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9102,7 +9166,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9112,19 +9176,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>42 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9137,12 +9201,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9155,12 +9219,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>5.27pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
           <t>5.42pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>5.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9173,7 +9237,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9268,7 +9332,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.43pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9278,19 +9342,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>35 min · 12 km · live traffic</t>
+          <t>23 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.00pm</t>
+          <t>10.48pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9303,7 +9367,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.00am (+1)</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9494,7 +9558,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9504,7 +9568,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>42 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9589,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9543,12 +9607,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9561,12 +9625,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>5.27pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
           <t>5.42pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>5.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9579,7 +9643,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9674,7 +9738,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.43pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9684,19 +9748,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>35 min · 12 km · live traffic</t>
+          <t>23 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.00pm</t>
+          <t>10.48pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9709,7 +9773,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.00am (+1)</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>30 h 32 over 16 show days · 1258 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>28 h 47 over 16 show days · 1265 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>38 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 30</t>
+          <t>1 h 31</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.43pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.43pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>49 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.13pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 11</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15 h 32</t>
+          <t>14 h 41</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 32) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.09pm</t>
+          <t>7.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.10pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.13pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>23 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.18pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.18pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>28 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.23pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.09pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>29 min · 8 km · traffic, refreshed hourly</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>42 min · 10 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.27pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.27pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.27pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.27pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
+          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 32) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>8 h · 393 km · traffic, refreshed hourly · home about 5.35am (+1)</t>
+          <t>7 h 21 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>58 min · 16 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>57 min · 13 km · typical traffic for the day</t>
+          <t>57 min · 13 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6338,19 +6338,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7002,14 +7002,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>55 min · 33 km · typical traffic for the day</t>
+          <t>53 min · 33 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139428</v>
+        <v>139849</v>
       </c>
     </row>
   </sheetData>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>28 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8583,12 +8583,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8601,12 +8601,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9176,19 +9176,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9201,12 +9201,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9237,7 +9237,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.43pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9342,19 +9342,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>23 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.48pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9367,7 +9367,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9625,12 +9625,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9643,7 +9643,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.43pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9748,19 +9748,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>23 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.48pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9773,7 +9773,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>28 h 47 over 16 show days · 1265 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>28 h 08 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.30am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>43 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>21 min</t>
+          <t>22 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 31</t>
+          <t>1 h 36</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.06pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 10</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,16 +1250,16 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>17 min</t>
+          <t>18 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 41</t>
+          <t>14 h 33</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1473,21 +1473,21 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>12.52pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.17pm</t>
+          <t>6.46pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 55</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.06pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.10pm</t>
+          <t>7.11pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>8.11pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.10pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.49pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.49pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.46am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.46am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>8 min · 4 km · live traffic · 10 min loading first</t>
+          <t>9 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4190,12 +4190,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>19 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 401 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 06 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>12.22pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -6008,12 +6008,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.22pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>12.52pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6026,12 +6026,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>12.52pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>58 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,146 +6098,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>3.42pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>3.42pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>BALINESE DANCE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Performance · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>5.50pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>6.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>7.17pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 13 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>6.46pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>26 min · 13 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6328,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6338,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>43 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.38pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7002,7 +7020,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>53 min · 33 km · typical traffic for the day</t>
+          <t>53 min · 33 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139849</v>
+        <v>139916</v>
       </c>
     </row>
   </sheetData>
@@ -7584,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7594,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.54am</t>
+          <t>5.56am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7615,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7633,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7651,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7768,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7778,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8008,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8047,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8065,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8083,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8350,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8360,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8381,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8399,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8417,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8435,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8552,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8562,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>42 min · 29 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.02pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8583,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8601,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8619,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8754,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8764,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic</t>
+          <t>35 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
+          <t>12.30am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9332,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9342,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9367,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9738,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9748,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9773,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>28 h 08 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 56 over 16 show days · 1271 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.30am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>43 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>21 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 36</t>
+          <t>1 h 27</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.06pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 10</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>18 min</t>
+          <t>17 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 33</t>
+          <t>14 h 52</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,16 +1478,16 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.46pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.06pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.11pm</t>
+          <t>7.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.11pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.10pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.49pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>8.49pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.46am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.46am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.25pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>9 min · 4 km · live traffic · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4190,12 +4190,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>13 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.09pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>15 min · 8 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>19 min · 10 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 06 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 10 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.46pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>43 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.38pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.56am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>12.58pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.25pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>35 min · 20 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.30am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.28am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 56 over 16 show days · 1271 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>26 h 54 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>38 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -913,11 +913,11 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 27</t>
+          <t>1 h 30</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 52</t>
+          <t>14 h 00</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.49pm</t>
+          <t>7.51pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.49pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>31 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.26pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.26pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 6 km · live traffic</t>
+          <t>14 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.09pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 10 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>6 h 52 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>53 min · 33 km · traffic, refreshed hourly</t>
+          <t>35 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>31 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.23pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>33 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
           <t>12.28am (+1)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9368,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9378,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9403,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9774,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9784,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9809,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>26 h 54 over 16 show days · 1274 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 14 over 16 show days · 1272 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.27am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.22pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 30</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 09</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>34 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 00</t>
+          <t>14 h 47</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.45pm</t>
+          <t>6.44pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.10pm</t>
+          <t>7.09pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.10pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.51pm</t>
+          <t>7.49pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.49pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>31 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.26pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.26pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>14 min · 6 km · live traffic</t>
+          <t>13 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.09pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 52 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 11 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.45pm</t>
+          <t>6.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>35 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>12.55pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.23pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>33 min · 20 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.22pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>32 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.27am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 14 over 16 show days · 1272 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 22 over 16 show days · 1263 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 29</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>49 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 47</t>
+          <t>14 h 51</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,11 +1483,11 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>49 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 6 km · live traffic</t>
+          <t>13 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 11 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 25 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>35 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.55pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.25pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.22pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>32 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.22pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
           <t>12.27am (+1)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 22 over 16 show days · 1263 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 05 over 16 show days · 1264 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>38 min</t>
+          <t>37 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 29</t>
+          <t>1 h 27</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.43pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1211,11 +1211,11 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 51</t>
+          <t>14 h 42</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.43pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>23 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.49pm</t>
+          <t>7.48pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.49pm</t>
+          <t>8.48pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.48pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>17 min · 10 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 25 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 21 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>37 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.32pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>35 min · 33 km · live traffic</t>
+          <t>34 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.54am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.55am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>15 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.55am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.05am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.05am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.15am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.15am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.00pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 05 over 16 show days · 1264 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 40 over 16 show days · 1261 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.27am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>37 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>21 min</t>
+          <t>23 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.22pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 27</t>
+          <t>1 h 28</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>49 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.43pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.31pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>17 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>36 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 42</t>
+          <t>14 h 35</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,16 +1478,16 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.44pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>49 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>34 min</t>
+          <t>36 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.09pm</t>
+          <t>7.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.10pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.43pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>23 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.48pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.48pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.48pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>8 min · 4 km · live traffic · 10 min loading first</t>
+          <t>9 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4190,12 +4190,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>9 min · 4 km · live traffic</t>
+          <t>11 min · 4 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>8.36pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.36pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.34pm</t>
+          <t>10.36pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.09pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>19 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 20 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.44pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>37 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>34 min · 33 km · live traffic</t>
+          <t>36 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.04pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.55am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>15 min · 11 km · live traffic · 10 min loading first</t>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.55am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.05am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.05am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>12.58pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.22pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 20 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.27am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.28am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>25 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 40 over 16 show days · 1261 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 18 over 16 show days · 1262 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.30am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>23 min</t>
+          <t>21 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 28</t>
+          <t>1 h 34</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 09</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.31pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>18 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>36 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 09</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 35</t>
+          <t>14 h 22</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>9 min · 4 km · live traffic · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4190,12 +4190,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.31pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>11 min · 4 km · live traffic</t>
+          <t>10 min · 4 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.36pm</t>
+          <t>8.35pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.36pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.36pm</t>
+          <t>10.35pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>13 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.09pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>19 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 20 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 01 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.05pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>42 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.25pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>35 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.23pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>33 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.28am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.30am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9212,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9237,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9255,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9273,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9594,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9604,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9643,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9661,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9679,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 18 over 16 show days · 1262 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>26 h 59 over 16 show days · 1259 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.30am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.27am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>37 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.22pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 34</t>
+          <t>1 h 22</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>49 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>18 min</t>
+          <t>17 min</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1347,11 +1347,11 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>34 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 22</t>
+          <t>14 h 43</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.45pm</t>
+          <t>6.44pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>49 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>36 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.10pm</t>
+          <t>7.09pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.10pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.10pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.49pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>8.49pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.25pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>10 min · 4 km · live traffic</t>
+          <t>9 min · 4 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.35pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.35pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic</t>
+          <t>13 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>15 min · 8 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 01 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 05 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.45pm</t>
+          <t>6.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 12 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>37 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.32pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>36 min · 33 km · live traffic</t>
+          <t>33 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.54am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>29 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic</t>
+          <t>34 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.02pm</t>
+          <t>12.54pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.25pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>35 min · 20 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.30am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.22pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>32 min · 20 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.27am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>26 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>26 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.45pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic</t>
+          <t>24 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>26 h 59 over 16 show days · 1259 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 32 over 16 show days · 1261 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.27am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>37 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>21 min</t>
+          <t>22 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.22pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 22</t>
+          <t>1 h 32</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>49 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 10</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 43</t>
+          <t>14 h 33</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.44pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>49 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.09pm</t>
+          <t>7.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.10pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.10pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.49pm</t>
+          <t>7.51pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.49pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>31 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.26pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.26pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 6 km · live traffic</t>
+          <t>14 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.09pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 05 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 07 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.44pm</t>
+          <t>6.45pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>25 min · 12 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>37 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>33 min · 33 km · live traffic</t>
+          <t>35 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 17 km · live traffic</t>
+          <t>31 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.04pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>34 min · 26 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.54pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.24pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.23pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.22pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 20 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.27am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.28am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9212,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>26 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9237,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9255,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9273,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9368,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9378,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9403,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9594,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9604,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9643,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9661,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9679,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9774,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9784,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 12 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9809,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 32 over 16 show days · 1261 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 15 over 16 show days · 1262 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.26am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>38 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.21pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 32</t>
+          <t>1 h 28</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 10</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>34 min</t>
+          <t>33 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 33</t>
+          <t>14 h 41</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.44pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.51pm</t>
+          <t>7.49pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.49pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>31 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.26pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.26pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>14 min · 6 km · live traffic</t>
+          <t>13 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.09pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 07 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 12 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139916</v>
+        <v>139849</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 17 km · live traffic</t>
+          <t>30 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.21pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic</t>
+          <t>31 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.28am (+1)</t>
+          <t>12.26am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.44pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>24 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.49pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.49pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 15 over 16 show days · 1262 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 48 over 16 show days · 1268 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.26am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.28am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.21pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 28</t>
+          <t>1 h 31</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 11</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1347,11 +1347,11 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>33 min</t>
+          <t>34 min</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 41</t>
+          <t>14 h 38</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.44pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.49pm</t>
+          <t>7.51pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.49pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.46am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.46am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>32 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.25pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 6 km · live traffic</t>
+          <t>13 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>19 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 12 · 401 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 16 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139849</v>
+        <v>139916</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.54am</t>
+          <t>5.56am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 17 km · live traffic</t>
+          <t>32 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 12 km · live traffic · 10 min loading first</t>
+          <t>17 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.21pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>31 min · 20 km · live traffic</t>
+          <t>33 min · 21 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.26am (+1)</t>
+          <t>12.28am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.44pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.49pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.49pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 48 over 16 show days · 1268 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 40 over 16 show days · 1284 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>38 min</t>
+          <t>39 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>23 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1 h 31</t>
+          <t>1 h 32</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.47pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.47pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.47pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 38</t>
+          <t>14 h 30</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,11 +1571,11 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>36 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J29" s="9" t="inlineStr"/>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 17 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.46pm</t>
+          <t>7.47pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>27 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.51pm</t>
+          <t>7.52pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.52pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.46am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>27 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.22pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.46am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 17 km · live traffic</t>
+          <t>33 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.28pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
+          <t>10.28pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>11.28pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic</t>
+          <t>14 min · 6 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.08pm</t>
+          <t>9.09pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>10.09pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>19 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 16 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 17 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>35 min · 33 km · live traffic</t>
+          <t>36 min · 34 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.56am</t>
+          <t>5.55am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 17 km · live traffic</t>
+          <t>33 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 8 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic</t>
+          <t>33 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.47pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>27 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.52pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.52pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>9.47pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic</t>
+          <t>27 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.51pm</t>
+          <t>9.52pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.51pm</t>
+          <t>10.52pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-citadel-sarovar-portico.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>27 h 40 over 16 show days · 1284 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>27 h 25 over 16 show days · 1271 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>39 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,16 +816,16 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>23 min</t>
+          <t>21 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.47pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 11</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,16 +1250,16 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 30</t>
+          <t>14 h 23</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 14) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>36 min</t>
+          <t>37 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J29" s="9" t="inlineStr"/>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.47pm</t>
+          <t>7.46pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.52pm</t>
+          <t>7.51pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>33 min · 17 km · live traffic</t>
+          <t>32 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.28pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.28pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.28pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>14 min · 6 km · live traffic</t>
+          <t>13 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>9.08pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.09pm</t>
+          <t>10.08pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 14 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 14) and back (5 h 50). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 14 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 17 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 09 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.17pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>36 min · 34 km · live traffic</t>
+          <t>37 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139916</v>
+        <v>139849</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.55am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>33 min · 17 km · live traffic</t>
+          <t>32 min · 18 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,19 +8026,19 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>13 min · 8 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.05pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.52pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.47pm</t>
+          <t>9.46pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic</t>
+          <t>26 min · 13 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.52pm</t>
+          <t>9.51pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.52pm</t>
+          <t>10.51pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
